--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_41.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4528230.888101422</v>
+        <v>4487876.232898024</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6764066.245458336</v>
+        <v>6764066.24545834</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6764066.245458336</v>
+        <v>6764066.24545834</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3307259.142253664</v>
+        <v>3307259.142253663</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3307259.142253664</v>
+        <v>3307259.142253663</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47441213.28808977</v>
+        <v>47441213.28808978</v>
       </c>
     </row>
   </sheetData>
@@ -669,52 +669,52 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H2" t="n">
-        <v>104.5000915779626</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>419.7382696589336</v>
+        <v>798.7814999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>66.13418277954936</v>
+        <v>66.13418277950457</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>298.9910820919849</v>
+        <v>815</v>
       </c>
       <c r="N2" t="n">
-        <v>195.5855355810472</v>
+        <v>815</v>
       </c>
       <c r="O2" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>601.8153451151099</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>798.7814999999999</v>
+        <v>701.1302324470771</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>494.8481678023229</v>
+        <v>442.2171995050529</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
-        <v>649.2212965486107</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V2" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
         <v>238.3734759809475</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>205.6080289096677</v>
+        <v>499.7520693989014</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -796,13 +796,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75737228701621</v>
+        <v>101.2075636724302</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -921,31 +921,31 @@
         <v>98.12488247690067</v>
       </c>
       <c r="L5" t="n">
-        <v>783.0093003026393</v>
+        <v>815</v>
       </c>
       <c r="M5" t="n">
-        <v>298.9910820919849</v>
+        <v>815</v>
       </c>
       <c r="N5" t="n">
-        <v>409.2117696382473</v>
+        <v>195.5855355810472</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>815</v>
+        <v>53.81572750974624</v>
       </c>
       <c r="Q5" t="n">
-        <v>371.9706110579117</v>
+        <v>798.7814999999999</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>284.1257731139787</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -960,7 +960,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>67.51997340159451</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>66.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1033,13 +1033,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>115.05352716151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1140,52 +1140,52 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H8" t="n">
-        <v>408.0096587035274</v>
+        <v>104.5000915779627</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>715.717186495642</v>
+        <v>783.0093003026253</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M8" t="n">
         <v>298.9910820919849</v>
       </c>
       <c r="N8" t="n">
-        <v>195.5855355810472</v>
+        <v>195.5855355810484</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>371.9706110579117</v>
+        <v>683.7217275920113</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>442.2171995050529</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>249.2212965486107</v>
+        <v>649.2212965486107</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1194,7 +1194,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
         <v>111.3174326828064</v>
@@ -1207,25 +1207,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>118.0893820455458</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>125.2313808393935</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1380,10 +1380,10 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1425,16 +1425,16 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>413.3734759809475</v>
+        <v>309.6442605072141</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>236.9378896911374</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1568,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>340.7767994885276</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         <v>170.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>134.7893471252638</v>
+        <v>131.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>125.3632896068686</v>
@@ -1623,7 +1623,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.450191385413969</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1796,19 +1796,19 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>16.34743437468335</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>338.6387678008247</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2039,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>338.6387678008247</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         <v>202.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>170.4745782429939</v>
+        <v>173.9247696284079</v>
       </c>
       <c r="D20" t="n">
         <v>131.3391557398498</v>
@@ -2097,7 +2097,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2270,19 +2270,19 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>47.21655408469291</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>132.4598500889414</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S23" t="n">
         <v>215.8481678023229</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>339.4016293563778</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>339.4016293563778</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>245.2212105579686</v>
       </c>
       <c r="C26" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
         <v>269.8481678023229</v>
@@ -2610,13 +2610,13 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>136.8735619684804</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>286.3174326828064</v>
@@ -2796,13 +2796,13 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>153.3632896068686</v>
+        <v>88.76134069083864</v>
       </c>
       <c r="F29" t="n">
-        <v>153.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>25.35659017828095</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>335.6755817285639</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>474.839266425598</v>
+        <v>52.97841917455702</v>
       </c>
       <c r="R31" t="n">
-        <v>53.74128073011016</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         <v>193.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>151.2159696284084</v>
+        <v>161.4745782429939</v>
       </c>
       <c r="D32" t="n">
         <v>122.3391557398498</v>
@@ -3039,7 +3039,7 @@
         <v>116.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>115.7573722870162</v>
+        <v>105.4987636724307</v>
       </c>
       <c r="H32" t="n">
         <v>120.0096587035274</v>
@@ -3054,13 +3054,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>47.83862152372274</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>47.83862152378481</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3209,28 +3209,28 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5207738011430365</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>135.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>47.88501458441813</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>283.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>352.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>380.9819279128893</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>74.37347970285543</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>47.83862152366675</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>47.83862152375353</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>206.8481678023229</v>
+        <v>196.5895591877376</v>
       </c>
       <c r="T35" t="n">
         <v>298.6755817285639</v>
       </c>
       <c r="U35" t="n">
-        <v>350.9626879340248</v>
+        <v>361.2212965486107</v>
       </c>
       <c r="V35" t="n">
         <v>341.8510241668239</v>
@@ -3458,19 +3458,19 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>352.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>399.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>142.0640741896034</v>
+        <v>437.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>17.51614119014671</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>47.55156149518377</v>
+        <v>47.83862153584505</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3695,19 +3695,19 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>56.67037184302036</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q40" t="n">
         <v>437.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>17.51614119014671</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>286.9993129555745</v>
+        <v>229.6957888009625</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3783,10 +3783,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>55.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>298.4232424760055</v>
+        <v>299.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>391.6755817285639</v>
@@ -3862,16 +3862,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>170.3581429114945</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>271.5639999646113</v>
+        <v>217.5960513602861</v>
       </c>
       <c r="T42" t="n">
         <v>210.3577652175138</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>205.2103597601867</v>
       </c>
       <c r="V42" t="n">
         <v>219.5106671915202</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>33.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>93.76761959483913</v>
+        <v>365.8613892860918</v>
       </c>
       <c r="C44" t="n">
-        <v>334.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>295.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>293.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>135.8785988282945</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4032,7 +4032,7 @@
         <v>534.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>514.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>523.3734759809475</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>269.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -4063,13 +4063,13 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>224.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>217.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>58.07926509047959</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>432.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>167.3078609832905</v>
       </c>
       <c r="T45" t="n">
         <v>290.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>285.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>299.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>120.7596963746418</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>304.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>284.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4187,10 +4187,10 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>35.95839127445794</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>78.1444032459268</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>395.9123998438258</v>
+        <v>1106.528124213083</v>
       </c>
       <c r="C2" t="n">
-        <v>345.9380783862562</v>
+        <v>1056.553802755514</v>
       </c>
       <c r="D2" t="n">
-        <v>335.4944867298423</v>
+        <v>1046.1102110991</v>
       </c>
       <c r="E2" t="n">
-        <v>331.0871234905811</v>
+        <v>1041.702847859838</v>
       </c>
       <c r="F2" t="n">
-        <v>326.1481045935994</v>
+        <v>1036.763828962857</v>
       </c>
       <c r="G2" t="n">
-        <v>322.3527790511588</v>
+        <v>628.9280993800121</v>
       </c>
       <c r="H2" t="n">
         <v>216.7971309926107</v>
@@ -4321,52 +4321,52 @@
         <v>65.2</v>
       </c>
       <c r="J2" t="n">
-        <v>448.0719498394611</v>
+        <v>65.2</v>
       </c>
       <c r="K2" t="n">
-        <v>1156.448952311256</v>
+        <v>773.5770024717956</v>
       </c>
       <c r="L2" t="n">
-        <v>1963.298952311256</v>
+        <v>1580.427002471796</v>
       </c>
       <c r="M2" t="n">
-        <v>2468.137758278947</v>
+        <v>1564.044679239472</v>
       </c>
       <c r="N2" t="n">
-        <v>3077.426611227384</v>
+        <v>1547.662356007149</v>
       </c>
       <c r="O2" t="n">
-        <v>3061.044287995061</v>
+        <v>2354.512356007149</v>
       </c>
       <c r="P2" t="n">
-        <v>3260</v>
+        <v>3161.362356007149</v>
       </c>
       <c r="Q2" t="n">
         <v>3260</v>
       </c>
       <c r="R2" t="n">
-        <v>3006.587273910814</v>
+        <v>3260</v>
       </c>
       <c r="S2" t="n">
-        <v>2506.740639767053</v>
+        <v>2813.315960095906</v>
       </c>
       <c r="T2" t="n">
-        <v>2318.179446101837</v>
+        <v>2220.714362390286</v>
       </c>
       <c r="U2" t="n">
-        <v>1662.400358678998</v>
+        <v>1968.975679007851</v>
       </c>
       <c r="V2" t="n">
-        <v>1026.187202954933</v>
+        <v>1736.80292732419</v>
       </c>
       <c r="W2" t="n">
-        <v>785.4059140852892</v>
+        <v>1496.021638454547</v>
       </c>
       <c r="X2" t="n">
-        <v>591.1818398825944</v>
+        <v>1301.797564251852</v>
       </c>
       <c r="Y2" t="n">
-        <v>478.7399886878405</v>
+        <v>1189.355713057098</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="C3" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="D3" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="E3" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="F3" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="G3" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="H3" t="n">
         <v>65.2</v>
@@ -4421,31 +4421,31 @@
         <v>1220.632420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1220.632420368536</v>
+        <v>1045.804879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1012.947542682003</v>
+        <v>541.0048097732011</v>
       </c>
       <c r="S3" t="n">
-        <v>945.7111790813851</v>
+        <v>473.7684461725837</v>
       </c>
       <c r="T3" t="n">
-        <v>940.2992950232904</v>
+        <v>468.356562114489</v>
       </c>
       <c r="U3" t="n">
-        <v>940.0868104170411</v>
+        <v>468.1440775082397</v>
       </c>
       <c r="V3" t="n">
-        <v>925.429570829647</v>
+        <v>453.4868379208456</v>
       </c>
       <c r="W3" t="n">
-        <v>488.6890224358807</v>
+        <v>420.7866935674835</v>
       </c>
       <c r="X3" t="n">
-        <v>468.6256492587216</v>
+        <v>400.7233203903244</v>
       </c>
       <c r="Y3" t="n">
-        <v>65.2</v>
+        <v>400.7233203903244</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>288.3666383453244</v>
+        <v>440.0757524108052</v>
       </c>
       <c r="C4" t="n">
-        <v>414.3686441637602</v>
+        <v>566.077758229241</v>
       </c>
       <c r="D4" t="n">
-        <v>527.6877882887603</v>
+        <v>679.3969023542411</v>
       </c>
       <c r="E4" t="n">
-        <v>645.5166925001733</v>
+        <v>797.2258065656541</v>
       </c>
       <c r="F4" t="n">
-        <v>645.5166925001733</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="G4" t="n">
-        <v>798.9232583870586</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="H4" t="n">
-        <v>968.4398435464561</v>
+        <v>1244.509930203872</v>
       </c>
       <c r="I4" t="n">
-        <v>1104.559068487504</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="J4" t="n">
         <v>1465.642809139955</v>
@@ -4506,25 +4506,25 @@
         <v>65.2</v>
       </c>
       <c r="S4" t="n">
-        <v>65.2</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>65.2</v>
+        <v>290.525934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>65.2</v>
+        <v>290.525934252978</v>
       </c>
       <c r="V4" t="n">
-        <v>65.2</v>
+        <v>290.525934252978</v>
       </c>
       <c r="W4" t="n">
-        <v>65.2</v>
+        <v>290.525934252978</v>
       </c>
       <c r="X4" t="n">
-        <v>65.2</v>
+        <v>290.525934252978</v>
       </c>
       <c r="Y4" t="n">
-        <v>176.6093006790323</v>
+        <v>328.3184147445131</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>954.9309932204726</v>
+        <v>1053.365529973416</v>
       </c>
       <c r="C5" t="n">
-        <v>904.9566717629029</v>
+        <v>1003.391208515846</v>
       </c>
       <c r="D5" t="n">
-        <v>490.472676066085</v>
+        <v>992.9476168594324</v>
       </c>
       <c r="E5" t="n">
-        <v>82.02490878641969</v>
+        <v>988.5402536201711</v>
       </c>
       <c r="F5" t="n">
-        <v>77.08588988943801</v>
+        <v>579.5608306827854</v>
       </c>
       <c r="G5" t="n">
-        <v>73.29056434699739</v>
+        <v>477.3309683874014</v>
       </c>
       <c r="H5" t="n">
         <v>65.2</v>
@@ -4564,19 +4564,19 @@
         <v>1155.805906933501</v>
       </c>
       <c r="L5" t="n">
-        <v>1140.066629078932</v>
+        <v>1139.423583701177</v>
       </c>
       <c r="M5" t="n">
-        <v>1644.905435046624</v>
+        <v>1091.370467768479</v>
       </c>
       <c r="N5" t="n">
-        <v>2038.410213189809</v>
+        <v>1700.659320716916</v>
       </c>
       <c r="O5" t="n">
-        <v>2845.260213189809</v>
+        <v>2507.509320716916</v>
       </c>
       <c r="P5" t="n">
-        <v>2828.877889957487</v>
+        <v>3260</v>
       </c>
       <c r="Q5" t="n">
         <v>3260</v>
@@ -4585,25 +4585,25 @@
         <v>3260</v>
       </c>
       <c r="S5" t="n">
-        <v>3164.193769896644</v>
+        <v>2760.153365856239</v>
       </c>
       <c r="T5" t="n">
-        <v>2877.198039478483</v>
+        <v>2167.551768150619</v>
       </c>
       <c r="U5" t="n">
-        <v>2625.459356096048</v>
+        <v>1915.813084768184</v>
       </c>
       <c r="V5" t="n">
-        <v>2393.286604412388</v>
+        <v>1683.640333084523</v>
       </c>
       <c r="W5" t="n">
-        <v>2152.505315542744</v>
+        <v>1442.859044214879</v>
       </c>
       <c r="X5" t="n">
-        <v>1958.281241340049</v>
+        <v>1248.634970012185</v>
       </c>
       <c r="Y5" t="n">
-        <v>1441.798986104891</v>
+        <v>1136.193118817431</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>411.3334315372855</v>
+        <v>352.7215750433768</v>
       </c>
       <c r="C6" t="n">
-        <v>411.3334315372855</v>
+        <v>352.7215750433768</v>
       </c>
       <c r="D6" t="n">
-        <v>411.3334315372855</v>
+        <v>352.7215750433768</v>
       </c>
       <c r="E6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="F6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="G6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="H6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="I6" t="n">
         <v>65.2</v>
@@ -4658,31 +4658,31 @@
         <v>1220.632420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1220.632420368536</v>
+        <v>1045.804879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1071.871008962092</v>
+        <v>897.0434684666577</v>
       </c>
       <c r="S6" t="n">
-        <v>1004.634645361474</v>
+        <v>425.7667008256362</v>
       </c>
       <c r="T6" t="n">
-        <v>999.2227613033796</v>
+        <v>420.3548167675414</v>
       </c>
       <c r="U6" t="n">
-        <v>999.0102766971303</v>
+        <v>420.1423321612922</v>
       </c>
       <c r="V6" t="n">
-        <v>984.3530371097362</v>
+        <v>405.4850925738981</v>
       </c>
       <c r="W6" t="n">
-        <v>547.6124887159699</v>
+        <v>372.784948220536</v>
       </c>
       <c r="X6" t="n">
-        <v>527.5491155388107</v>
+        <v>352.7215750433768</v>
       </c>
       <c r="Y6" t="n">
-        <v>411.3334315372855</v>
+        <v>352.7215750433768</v>
       </c>
     </row>
     <row r="7">
@@ -4692,19 +4692,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>440.0757524108052</v>
+        <v>717.8432908896259</v>
       </c>
       <c r="C7" t="n">
-        <v>566.077758229241</v>
+        <v>843.8452967080617</v>
       </c>
       <c r="D7" t="n">
-        <v>679.3969023542411</v>
+        <v>957.1644408330618</v>
       </c>
       <c r="E7" t="n">
-        <v>797.2258065656541</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="F7" t="n">
-        <v>921.5867791575896</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="G7" t="n">
         <v>1074.993345044475</v>
@@ -4749,19 +4749,19 @@
         <v>290.525934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>440.0757524108052</v>
+        <v>290.525934252978</v>
       </c>
       <c r="V7" t="n">
-        <v>440.0757524108052</v>
+        <v>290.525934252978</v>
       </c>
       <c r="W7" t="n">
-        <v>440.0757524108052</v>
+        <v>343.6458615201079</v>
       </c>
       <c r="X7" t="n">
-        <v>440.0757524108052</v>
+        <v>494.6766525443015</v>
       </c>
       <c r="Y7" t="n">
-        <v>440.0757524108052</v>
+        <v>606.0859532233337</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>702.4877201726792</v>
+        <v>1203.993207924634</v>
       </c>
       <c r="C8" t="n">
-        <v>652.5133987151096</v>
+        <v>1154.018886467064</v>
       </c>
       <c r="D8" t="n">
-        <v>642.0698070586957</v>
+        <v>1143.575294810651</v>
       </c>
       <c r="E8" t="n">
-        <v>637.6624438194344</v>
+        <v>1139.167931571389</v>
       </c>
       <c r="F8" t="n">
-        <v>632.7234249224528</v>
+        <v>730.1885086340036</v>
       </c>
       <c r="G8" t="n">
-        <v>628.9280993800121</v>
+        <v>322.3527790511589</v>
       </c>
       <c r="H8" t="n">
         <v>216.7971309926107</v>
@@ -4795,52 +4795,52 @@
         <v>65.2</v>
       </c>
       <c r="J8" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K8" t="n">
-        <v>117.4325542736812</v>
+        <v>432.332671984893</v>
       </c>
       <c r="L8" t="n">
-        <v>924.2825542736812</v>
+        <v>415.9503487525697</v>
       </c>
       <c r="M8" t="n">
-        <v>1429.121360241373</v>
+        <v>920.7891547202616</v>
       </c>
       <c r="N8" t="n">
-        <v>2038.41021318981</v>
+        <v>1530.078007668699</v>
       </c>
       <c r="O8" t="n">
-        <v>2845.26021318981</v>
+        <v>2336.928007668699</v>
       </c>
       <c r="P8" t="n">
-        <v>2828.877889957487</v>
+        <v>3143.778007668699</v>
       </c>
       <c r="Q8" t="n">
         <v>3260</v>
       </c>
       <c r="R8" t="n">
-        <v>3260</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>2813.315960095906</v>
+        <v>2910.781043807457</v>
       </c>
       <c r="T8" t="n">
-        <v>2220.714362390286</v>
+        <v>2722.219850142241</v>
       </c>
       <c r="U8" t="n">
-        <v>1968.975679007851</v>
+        <v>2066.440762719402</v>
       </c>
       <c r="V8" t="n">
-        <v>1736.80292732419</v>
+        <v>1834.268011035741</v>
       </c>
       <c r="W8" t="n">
-        <v>1496.021638454547</v>
+        <v>1593.486722166097</v>
       </c>
       <c r="X8" t="n">
-        <v>897.7571602114477</v>
+        <v>1399.262647963403</v>
       </c>
       <c r="Y8" t="n">
-        <v>785.3153090166938</v>
+        <v>1286.820796768649</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527.5491155388108</v>
+        <v>543.1485532697941</v>
       </c>
       <c r="C9" t="n">
-        <v>527.5491155388108</v>
+        <v>543.1485532697941</v>
       </c>
       <c r="D9" t="n">
-        <v>527.5491155388108</v>
+        <v>191.6963442822156</v>
       </c>
       <c r="E9" t="n">
-        <v>408.2669114524009</v>
+        <v>191.6963442822156</v>
       </c>
       <c r="F9" t="n">
-        <v>65.2</v>
+        <v>191.6963442822156</v>
       </c>
       <c r="G9" t="n">
-        <v>65.2</v>
+        <v>191.6963442822156</v>
       </c>
       <c r="H9" t="n">
         <v>65.2</v>
@@ -4916,10 +4916,10 @@
         <v>951.6528927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>527.5491155388108</v>
+        <v>931.5895195792149</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.5491155388108</v>
+        <v>931.5895195792149</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>870.5391829427149</v>
+        <v>810.1097405151413</v>
       </c>
       <c r="C10" t="n">
-        <v>870.5391829427149</v>
+        <v>936.1117463335771</v>
       </c>
       <c r="D10" t="n">
-        <v>983.858327067715</v>
+        <v>936.1117463335771</v>
       </c>
       <c r="E10" t="n">
-        <v>1101.687231279128</v>
+        <v>1053.94065054499</v>
       </c>
       <c r="F10" t="n">
-        <v>1226.048203871063</v>
+        <v>1053.94065054499</v>
       </c>
       <c r="G10" t="n">
-        <v>1226.048203871063</v>
+        <v>1207.347216431875</v>
       </c>
       <c r="H10" t="n">
-        <v>1244.509930203872</v>
+        <v>1376.863801591273</v>
       </c>
       <c r="I10" t="n">
-        <v>1465.642809139955</v>
+        <v>1376.863801591273</v>
       </c>
       <c r="J10" t="n">
-        <v>1465.642809139955</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="K10" t="n">
         <v>1576.007243076824</v>
@@ -4983,22 +4983,22 @@
         <v>65.2</v>
       </c>
       <c r="T10" t="n">
-        <v>253.2756791588048</v>
+        <v>65.2</v>
       </c>
       <c r="U10" t="n">
-        <v>499.8268717970915</v>
+        <v>65.2</v>
       </c>
       <c r="V10" t="n">
-        <v>698.6482646830375</v>
+        <v>264.0213928859459</v>
       </c>
       <c r="W10" t="n">
-        <v>870.5391829427149</v>
+        <v>435.9123111456233</v>
       </c>
       <c r="X10" t="n">
-        <v>870.5391829427149</v>
+        <v>586.9431021698168</v>
       </c>
       <c r="Y10" t="n">
-        <v>870.5391829427149</v>
+        <v>698.3524028488491</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>842.0350023209337</v>
+        <v>1207.456245745725</v>
       </c>
       <c r="C11" t="n">
-        <v>615.2930040956873</v>
+        <v>980.7142475204787</v>
       </c>
       <c r="D11" t="n">
-        <v>428.0817356715965</v>
+        <v>793.502979096388</v>
       </c>
       <c r="E11" t="n">
-        <v>246.9066956646585</v>
+        <v>612.32793908945</v>
       </c>
       <c r="F11" t="n">
-        <v>65.2</v>
+        <v>430.6212434247915</v>
       </c>
       <c r="G11" t="n">
-        <v>65.2</v>
+        <v>250.0582411146742</v>
       </c>
       <c r="H11" t="n">
         <v>65.2</v>
@@ -5041,16 +5041,16 @@
         <v>1973.065479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>2483.914308114459</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>3097.134627889222</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3260</v>
@@ -5059,25 +5059,25 @@
         <v>3233.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>2961.286094312508</v>
+        <v>3233.860001183541</v>
       </c>
       <c r="T11" t="n">
-        <v>2595.957223879615</v>
+        <v>2868.531130750648</v>
       </c>
       <c r="U11" t="n">
-        <v>2167.450863729503</v>
+        <v>2440.024770600536</v>
       </c>
       <c r="V11" t="n">
-        <v>1758.510435278166</v>
+        <v>2440.024770600536</v>
       </c>
       <c r="W11" t="n">
-        <v>1340.961469640845</v>
+        <v>2127.252790290219</v>
       </c>
       <c r="X11" t="n">
-        <v>1340.961469640845</v>
+        <v>1756.261039319847</v>
       </c>
       <c r="Y11" t="n">
-        <v>1101.630267932625</v>
+        <v>1467.051511357417</v>
       </c>
     </row>
     <row r="12">
@@ -5117,10 +5117,10 @@
         <v>831.6442142372473</v>
       </c>
       <c r="L12" t="n">
-        <v>1121.920378378698</v>
+        <v>1325.744675832447</v>
       </c>
       <c r="M12" t="n">
-        <v>1430.750920121558</v>
+        <v>1634.575217575307</v>
       </c>
       <c r="N12" t="n">
         <v>1786.781204729126</v>
@@ -5211,7 +5211,7 @@
         <v>409.4189893823511</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.2</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="R13" t="n">
         <v>65.2</v>
@@ -5251,19 +5251,19 @@
         <v>711.4720165966545</v>
       </c>
       <c r="D14" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E14" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F14" t="n">
-        <v>321.5303343338825</v>
+        <v>325.0153761373309</v>
       </c>
       <c r="G14" t="n">
-        <v>195.5127865692196</v>
+        <v>198.9978283726681</v>
       </c>
       <c r="H14" t="n">
-        <v>65.2</v>
+        <v>68.68504180344846</v>
       </c>
       <c r="I14" t="n">
         <v>65.2</v>
@@ -5272,22 +5272,22 @@
         <v>456.5091130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.215479385524</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1166.215479385524</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="M14" t="n">
-        <v>1677.064308114459</v>
+        <v>967.3579417665908</v>
       </c>
       <c r="N14" t="n">
-        <v>2014.550904947333</v>
+        <v>1580.578261541354</v>
       </c>
       <c r="O14" t="n">
-        <v>2821.400904947332</v>
+        <v>2387.428261541354</v>
       </c>
       <c r="P14" t="n">
-        <v>2821.400904947332</v>
+        <v>3194.278261541354</v>
       </c>
       <c r="Q14" t="n">
         <v>3260</v>
@@ -5351,19 +5351,19 @@
         <v>250.4113981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>439.6042142372473</v>
+        <v>593.7180986016792</v>
       </c>
       <c r="L15" t="n">
-        <v>710.9546758324475</v>
+        <v>865.0685601968793</v>
       </c>
       <c r="M15" t="n">
-        <v>797.0352175753068</v>
+        <v>951.1491019397386</v>
       </c>
       <c r="N15" t="n">
-        <v>930.3155021828751</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O15" t="n">
-        <v>1323.471838231026</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P15" t="n">
         <v>1712.211182700533</v>
@@ -5439,16 +5439,16 @@
         <v>859.3827230120968</v>
       </c>
       <c r="N16" t="n">
-        <v>859.3827230120968</v>
+        <v>842.8701630376692</v>
       </c>
       <c r="O16" t="n">
-        <v>859.3827230120968</v>
+        <v>477.7736336649268</v>
       </c>
       <c r="P16" t="n">
-        <v>859.3827230120968</v>
+        <v>65.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>517.3233615971224</v>
+        <v>65.2</v>
       </c>
       <c r="R16" t="n">
         <v>65.2</v>
@@ -5506,25 +5506,25 @@
         <v>65.2</v>
       </c>
       <c r="J17" t="n">
-        <v>456.5091130376557</v>
+        <v>180.775390095766</v>
       </c>
       <c r="K17" t="n">
-        <v>1166.215479385524</v>
+        <v>890.4817564436344</v>
       </c>
       <c r="L17" t="n">
-        <v>1973.065479385524</v>
+        <v>1697.331756443634</v>
       </c>
       <c r="M17" t="n">
-        <v>2483.914308114459</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N17" t="n">
-        <v>3097.134627889222</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>3097.134627889222</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>3097.134627889222</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>3260</v>
@@ -5582,28 +5582,28 @@
         <v>65.2</v>
       </c>
       <c r="I18" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>189.156520175299</v>
+        <v>526.6213981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>378.3493362696823</v>
+        <v>715.8142142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>865.0685601968794</v>
+        <v>987.1646758324473</v>
       </c>
       <c r="M18" t="n">
-        <v>1227.359101939739</v>
+        <v>1332.220629500164</v>
       </c>
       <c r="N18" t="n">
-        <v>1360.639386547307</v>
+        <v>1465.500914107732</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.681838231026</v>
+        <v>1704.543365791451</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.211182700533</v>
+        <v>1817.072710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1817.072710260958</v>
@@ -5682,10 +5682,10 @@
         <v>859.3827230120968</v>
       </c>
       <c r="P19" t="n">
-        <v>517.3233615971224</v>
+        <v>446.80908934717</v>
       </c>
       <c r="Q19" t="n">
-        <v>517.3233615971224</v>
+        <v>65.2</v>
       </c>
       <c r="R19" t="n">
         <v>65.2</v>
@@ -5722,22 +5722,22 @@
         <v>883.6685602764463</v>
       </c>
       <c r="C20" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D20" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E20" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F20" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G20" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H20" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I20" t="n">
         <v>65.2</v>
@@ -5746,19 +5746,19 @@
         <v>456.5091130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1166.215479385524</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1973.065479385524</v>
+        <v>696.8520762183977</v>
       </c>
       <c r="M20" t="n">
-        <v>1973.065479385524</v>
+        <v>1207.700904947333</v>
       </c>
       <c r="N20" t="n">
-        <v>2586.285799160287</v>
+        <v>1207.700904947333</v>
       </c>
       <c r="O20" t="n">
-        <v>2821.400904947332</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="P20" t="n">
         <v>2821.400904947332</v>
@@ -5822,22 +5822,22 @@
         <v>126.454877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>250.4113981428639</v>
+        <v>404.5252825072959</v>
       </c>
       <c r="K21" t="n">
-        <v>439.6042142372473</v>
+        <v>593.7180986016792</v>
       </c>
       <c r="L21" t="n">
-        <v>710.9546758324475</v>
+        <v>865.0685601968793</v>
       </c>
       <c r="M21" t="n">
-        <v>1073.245217575307</v>
+        <v>951.1491019397386</v>
       </c>
       <c r="N21" t="n">
-        <v>1206.525502182875</v>
+        <v>1084.429386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1599.681838231026</v>
+        <v>1323.471838231026</v>
       </c>
       <c r="P21" t="n">
         <v>1712.211182700533</v>
@@ -5913,16 +5913,16 @@
         <v>859.3827230120968</v>
       </c>
       <c r="N22" t="n">
-        <v>564.2462833437282</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O22" t="n">
-        <v>516.552794369291</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P22" t="n">
-        <v>516.552794369291</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.2</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="R22" t="n">
         <v>65.2</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C23" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D23" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E23" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F23" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G23" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H23" t="n">
         <v>65.2</v>
@@ -5980,52 +5980,52 @@
         <v>65.2</v>
       </c>
       <c r="J23" t="n">
-        <v>456.5091130376557</v>
+        <v>65.2</v>
       </c>
       <c r="K23" t="n">
-        <v>456.5091130376557</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="L23" t="n">
-        <v>1207.700904947333</v>
+        <v>1581.756366347868</v>
       </c>
       <c r="M23" t="n">
-        <v>1207.700904947333</v>
+        <v>2092.605195076803</v>
       </c>
       <c r="N23" t="n">
-        <v>1207.700904947333</v>
+        <v>2705.825514851566</v>
       </c>
       <c r="O23" t="n">
-        <v>2014.550904947333</v>
+        <v>3260</v>
       </c>
       <c r="P23" t="n">
-        <v>2821.400904947332</v>
+        <v>3260</v>
       </c>
       <c r="Q23" t="n">
         <v>3260</v>
       </c>
       <c r="R23" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S23" t="n">
-        <v>3041.971547674421</v>
+        <v>3038.486505870972</v>
       </c>
       <c r="T23" t="n">
-        <v>2731.188131786983</v>
+        <v>2727.703089983534</v>
       </c>
       <c r="U23" t="n">
-        <v>2357.227226182325</v>
+        <v>2353.742184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>2002.832252276443</v>
+        <v>1999.347210472994</v>
       </c>
       <c r="W23" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X23" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y23" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="24">
@@ -6056,28 +6056,28 @@
         <v>65.2</v>
       </c>
       <c r="I24" t="n">
-        <v>126.454877967565</v>
+        <v>109.2202898924221</v>
       </c>
       <c r="J24" t="n">
-        <v>250.4113981428639</v>
+        <v>233.176810067721</v>
       </c>
       <c r="K24" t="n">
-        <v>439.6042142372473</v>
+        <v>698.5796261621044</v>
       </c>
       <c r="L24" t="n">
-        <v>710.9546758324475</v>
+        <v>1246.140087757305</v>
       </c>
       <c r="M24" t="n">
-        <v>797.0352175753068</v>
+        <v>1332.220629500164</v>
       </c>
       <c r="N24" t="n">
-        <v>1084.429386547307</v>
+        <v>1465.500914107732</v>
       </c>
       <c r="O24" t="n">
-        <v>1599.681838231026</v>
+        <v>1704.543365791451</v>
       </c>
       <c r="P24" t="n">
-        <v>1712.211182700533</v>
+        <v>1817.072710260958</v>
       </c>
       <c r="Q24" t="n">
         <v>1817.072710260958</v>
@@ -6156,10 +6156,10 @@
         <v>859.3827230120968</v>
       </c>
       <c r="P25" t="n">
-        <v>516.552794369291</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.2</v>
+        <v>408.0299286428058</v>
       </c>
       <c r="R25" t="n">
         <v>65.2</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1204.576245745725</v>
+        <v>289.0619982252464</v>
       </c>
       <c r="C26" t="n">
-        <v>977.8342475204787</v>
+        <v>62.32</v>
       </c>
       <c r="D26" t="n">
-        <v>790.622979096388</v>
+        <v>62.32</v>
       </c>
       <c r="E26" t="n">
-        <v>609.44793908945</v>
+        <v>62.32</v>
       </c>
       <c r="F26" t="n">
-        <v>427.7412434247915</v>
+        <v>62.32</v>
       </c>
       <c r="G26" t="n">
-        <v>247.1782411146742</v>
+        <v>62.32</v>
       </c>
       <c r="H26" t="n">
         <v>62.32</v>
@@ -6220,16 +6220,16 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>1163.335479385524</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>1395.342076218372</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="M26" t="n">
-        <v>1906.190904947307</v>
+        <v>964.4779417665907</v>
       </c>
       <c r="N26" t="n">
-        <v>1906.190904947307</v>
+        <v>1577.698261541354</v>
       </c>
       <c r="O26" t="n">
         <v>1906.190904947307</v>
@@ -6241,28 +6241,28 @@
         <v>3116</v>
       </c>
       <c r="R26" t="n">
-        <v>3116</v>
+        <v>3089.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>2843.426093128967</v>
+        <v>2817.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2478.097222696074</v>
+        <v>2451.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2049.590862545962</v>
+        <v>2023.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>2049.590862545962</v>
+        <v>1614.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1632.041896908641</v>
+        <v>1196.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1493.785773708156</v>
+        <v>825.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>1204.576245745725</v>
+        <v>536.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6293,25 +6293,25 @@
         <v>62.32</v>
       </c>
       <c r="I27" t="n">
-        <v>70.11487796756495</v>
+        <v>62.32</v>
       </c>
       <c r="J27" t="n">
-        <v>416.8213981428639</v>
+        <v>409.026520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>828.7642142372474</v>
+        <v>820.9693362696823</v>
       </c>
       <c r="L27" t="n">
-        <v>1119.040378378698</v>
+        <v>1315.069797864883</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.870920121557</v>
+        <v>1623.900339607742</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.901204729126</v>
+        <v>1979.93062421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2245.693656412845</v>
+        <v>2441.723075899029</v>
       </c>
       <c r="P27" t="n">
         <v>2580.973000882351</v>
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>759.7172146222275</v>
+        <v>513.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>559.2378426596074</v>
+        <v>312.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>398.2892004981429</v>
+        <v>151.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>243.3767867538311</v>
+        <v>62.32</v>
       </c>
       <c r="F29" t="n">
-        <v>87.93271735179894</v>
+        <v>62.32</v>
       </c>
       <c r="G29" t="n">
         <v>62.32</v>
@@ -6454,19 +6454,19 @@
         <v>62.32</v>
       </c>
       <c r="J29" t="n">
-        <v>62.32</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>62.32</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>782.1217564436025</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>1292.970585172538</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="N29" t="n">
-        <v>1906.190904947301</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="O29" t="n">
         <v>1906.190904947301</v>
@@ -6481,25 +6481,25 @@
         <v>3116</v>
       </c>
       <c r="S29" t="n">
-        <v>3116</v>
+        <v>2869.688719391593</v>
       </c>
       <c r="T29" t="n">
-        <v>2776.933755829733</v>
+        <v>2530.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>2374.690021942248</v>
+        <v>2128.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1992.012219753537</v>
+        <v>1745.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>1600.725880378842</v>
+        <v>1354.414599770435</v>
       </c>
       <c r="X29" t="n">
-        <v>1255.996755671097</v>
+        <v>1009.68547506269</v>
       </c>
       <c r="Y29" t="n">
-        <v>993.0498539712927</v>
+        <v>746.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6536,22 +6536,22 @@
         <v>468.3013981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>657.4942142372473</v>
+        <v>905.9842142372472</v>
       </c>
       <c r="L30" t="n">
-        <v>1177.334675832447</v>
+        <v>1425.824675832447</v>
       </c>
       <c r="M30" t="n">
-        <v>1427.951526182163</v>
+        <v>1511.905217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1561.231810789731</v>
+        <v>1886.863338350157</v>
       </c>
       <c r="O30" t="n">
-        <v>2048.76426247345</v>
+        <v>2125.905790033876</v>
       </c>
       <c r="P30" t="n">
-        <v>2161.293606942957</v>
+        <v>2238.435134503382</v>
       </c>
       <c r="Q30" t="n">
         <v>2238.435134503382</v>
@@ -6633,7 +6633,7 @@
         <v>596.2397446017254</v>
       </c>
       <c r="Q31" t="n">
-        <v>116.6041219496062</v>
+        <v>542.7261898799507</v>
       </c>
       <c r="R31" t="n">
         <v>62.32</v>
@@ -6670,16 +6670,16 @@
         <v>812.3958330037195</v>
       </c>
       <c r="C32" t="n">
-        <v>659.6524293386606</v>
+        <v>649.2901984148368</v>
       </c>
       <c r="D32" t="n">
-        <v>536.0775245509335</v>
+        <v>525.7152936271098</v>
       </c>
       <c r="E32" t="n">
-        <v>418.5388481803591</v>
+        <v>408.1766172565353</v>
       </c>
       <c r="F32" t="n">
-        <v>300.4685161520642</v>
+        <v>290.1062852282405</v>
       </c>
       <c r="G32" t="n">
         <v>183.5418774783105</v>
@@ -6691,25 +6691,25 @@
         <v>62.32</v>
       </c>
       <c r="J32" t="n">
-        <v>453.6291130376557</v>
+        <v>62.32</v>
       </c>
       <c r="K32" t="n">
-        <v>1163.335479385524</v>
+        <v>772.0263663478684</v>
       </c>
       <c r="L32" t="n">
-        <v>1163.335479385524</v>
+        <v>771.0647617334016</v>
       </c>
       <c r="M32" t="n">
-        <v>1674.184308114459</v>
+        <v>1134.980904947242</v>
       </c>
       <c r="N32" t="n">
-        <v>1625.862468191444</v>
+        <v>1134.980904947242</v>
       </c>
       <c r="O32" t="n">
-        <v>2344.789999999954</v>
+        <v>1906.190904947287</v>
       </c>
       <c r="P32" t="n">
-        <v>3116</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>3116</v>
@@ -6767,28 +6767,28 @@
         <v>62.32</v>
       </c>
       <c r="I33" t="n">
-        <v>132.484877967565</v>
+        <v>62.32</v>
       </c>
       <c r="J33" t="n">
-        <v>256.4413981428639</v>
+        <v>471.3965201752989</v>
       </c>
       <c r="K33" t="n">
-        <v>445.6342142372473</v>
+        <v>660.5893362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>1002.104675832447</v>
+        <v>993.1249238332429</v>
       </c>
       <c r="M33" t="n">
-        <v>1088.185217575307</v>
+        <v>1079.205465576102</v>
       </c>
       <c r="N33" t="n">
-        <v>1326.257277744096</v>
+        <v>1212.48575018367</v>
       </c>
       <c r="O33" t="n">
-        <v>1565.299729427815</v>
+        <v>1451.528201867389</v>
       </c>
       <c r="P33" t="n">
-        <v>1677.829073897321</v>
+        <v>1564.057546336896</v>
       </c>
       <c r="Q33" t="n">
         <v>1677.829073897321</v>
@@ -6852,25 +6852,25 @@
         <v>965.3074096938342</v>
       </c>
       <c r="K34" t="n">
-        <v>964.7813755512655</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="L34" t="n">
-        <v>827.8645794322965</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="M34" t="n">
-        <v>779.4958778318742</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="N34" t="n">
-        <v>493.4503472544146</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="O34" t="n">
-        <v>137.4447269725813</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="P34" t="n">
-        <v>137.4447269725813</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="Q34" t="n">
-        <v>137.4447269725813</v>
+        <v>580.4771794787945</v>
       </c>
       <c r="R34" t="n">
         <v>137.4447269725813</v>
@@ -6931,22 +6931,22 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>1162.373874771059</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="L35" t="n">
-        <v>1162.373874771059</v>
+        <v>452.6675084231883</v>
       </c>
       <c r="M35" t="n">
-        <v>1673.222703499994</v>
+        <v>963.5163371521234</v>
       </c>
       <c r="N35" t="n">
-        <v>2286.443023274757</v>
+        <v>1576.736656926887</v>
       </c>
       <c r="O35" t="n">
-        <v>2677.400904947332</v>
+        <v>2344.78999999993</v>
       </c>
       <c r="P35" t="n">
-        <v>2677.400904947332</v>
+        <v>3116</v>
       </c>
       <c r="Q35" t="n">
         <v>3116</v>
@@ -6955,10 +6955,10 @@
         <v>3116</v>
       </c>
       <c r="S35" t="n">
-        <v>2907.06245676533</v>
+        <v>2917.424687689154</v>
       </c>
       <c r="T35" t="n">
-        <v>2605.369949968801</v>
+        <v>2615.732180892625</v>
       </c>
       <c r="U35" t="n">
         <v>2250.862184378877</v>
@@ -7004,25 +7004,25 @@
         <v>62.32</v>
       </c>
       <c r="I36" t="n">
-        <v>132.484877967565</v>
+        <v>123.5051259683604</v>
       </c>
       <c r="J36" t="n">
-        <v>256.4413981428639</v>
+        <v>247.4616461436594</v>
       </c>
       <c r="K36" t="n">
-        <v>445.6342142372473</v>
+        <v>436.6544622380428</v>
       </c>
       <c r="L36" t="n">
-        <v>716.9846758324475</v>
+        <v>708.0049238332429</v>
       </c>
       <c r="M36" t="n">
-        <v>803.0652175753067</v>
+        <v>1079.205465576102</v>
       </c>
       <c r="N36" t="n">
-        <v>936.3455021828751</v>
+        <v>1212.48575018367</v>
       </c>
       <c r="O36" t="n">
-        <v>1175.387953866594</v>
+        <v>1451.528201867389</v>
       </c>
       <c r="P36" t="n">
         <v>1564.057546336896</v>
@@ -7101,16 +7101,16 @@
         <v>965.3074096938342</v>
       </c>
       <c r="O37" t="n">
-        <v>609.3017894120009</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="P37" t="n">
-        <v>205.8190648379832</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="Q37" t="n">
-        <v>62.32</v>
+        <v>523.0455244154523</v>
       </c>
       <c r="R37" t="n">
-        <v>62.32</v>
+        <v>80.0130719092391</v>
       </c>
       <c r="S37" t="n">
         <v>62.32</v>
@@ -7168,19 +7168,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>1162.379644967591</v>
+        <v>1134.980904947154</v>
       </c>
       <c r="L38" t="n">
-        <v>1162.379644967591</v>
+        <v>1134.980904947154</v>
       </c>
       <c r="M38" t="n">
-        <v>1673.228473696526</v>
+        <v>1134.980904947154</v>
       </c>
       <c r="N38" t="n">
-        <v>2286.448793471289</v>
+        <v>1134.980904947154</v>
       </c>
       <c r="O38" t="n">
-        <v>2677.690864584385</v>
+        <v>1906.190904947243</v>
       </c>
       <c r="P38" t="n">
         <v>2677.400904947332</v>
@@ -7241,7 +7241,7 @@
         <v>62.32</v>
       </c>
       <c r="I39" t="n">
-        <v>132.484877967565</v>
+        <v>123.5051259683605</v>
       </c>
       <c r="J39" t="n">
         <v>532.5816461436594</v>
@@ -7338,16 +7338,16 @@
         <v>965.3074096938342</v>
       </c>
       <c r="O40" t="n">
-        <v>965.3074096938342</v>
+        <v>908.0646098523995</v>
       </c>
       <c r="P40" t="n">
-        <v>965.3074096938342</v>
+        <v>504.5818852783818</v>
       </c>
       <c r="Q40" t="n">
-        <v>523.0455244154523</v>
+        <v>62.32</v>
       </c>
       <c r="R40" t="n">
-        <v>80.0130719092391</v>
+        <v>62.32</v>
       </c>
       <c r="S40" t="n">
         <v>62.32</v>
@@ -7405,19 +7405,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>1163.335479385524</v>
+        <v>624.1320762181268</v>
       </c>
       <c r="L41" t="n">
-        <v>1553.331756443634</v>
+        <v>624.1320762181268</v>
       </c>
       <c r="M41" t="n">
-        <v>2064.180585172569</v>
+        <v>1134.980904947062</v>
       </c>
       <c r="N41" t="n">
-        <v>2677.400904947332</v>
+        <v>1134.980904947062</v>
       </c>
       <c r="O41" t="n">
-        <v>2677.400904947332</v>
+        <v>1906.190904947197</v>
       </c>
       <c r="P41" t="n">
         <v>2677.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>3116</v>
       </c>
       <c r="R41" t="n">
-        <v>3116</v>
+        <v>3059.556970880511</v>
       </c>
       <c r="S41" t="n">
-        <v>2814.562381337368</v>
+        <v>2756.680033706447</v>
       </c>
       <c r="T41" t="n">
-        <v>2418.930480601445</v>
+        <v>2361.048132970524</v>
       </c>
       <c r="U41" t="n">
-        <v>1960.121090148303</v>
+        <v>1902.238742517382</v>
       </c>
       <c r="V41" t="n">
-        <v>1520.877631393936</v>
+        <v>1462.995283763014</v>
       </c>
       <c r="W41" t="n">
-        <v>1073.025635453585</v>
+        <v>1015.143287822663</v>
       </c>
       <c r="X41" t="n">
-        <v>671.7308541801827</v>
+        <v>613.8485065492615</v>
       </c>
       <c r="Y41" t="n">
-        <v>352.2182959147218</v>
+        <v>294.3359482838005</v>
       </c>
     </row>
     <row r="42">
@@ -7490,28 +7490,28 @@
         <v>1225.969797864882</v>
       </c>
       <c r="M42" t="n">
-        <v>1505.100339607742</v>
+        <v>1395.151737666644</v>
       </c>
       <c r="N42" t="n">
-        <v>1831.43062421531</v>
+        <v>1721.482022274212</v>
       </c>
       <c r="O42" t="n">
-        <v>2263.523075899029</v>
+        <v>2153.574473957931</v>
       </c>
       <c r="P42" t="n">
-        <v>2456.761110822198</v>
+        <v>2459.153818427438</v>
       </c>
       <c r="Q42" t="n">
-        <v>2478.462638382623</v>
+        <v>2459.153818427438</v>
       </c>
       <c r="R42" t="n">
-        <v>2306.38370614879</v>
+        <v>2459.153818427438</v>
       </c>
       <c r="S42" t="n">
-        <v>2032.076635477466</v>
+        <v>2239.359827154422</v>
       </c>
       <c r="T42" t="n">
-        <v>1819.594044348664</v>
+        <v>2026.87723602562</v>
       </c>
       <c r="U42" t="n">
         <v>1819.594044348664</v>
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="C43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="D43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="E43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="F43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="G43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="H43" t="n">
-        <v>70.01905116866453</v>
+        <v>62.32</v>
       </c>
       <c r="I43" t="n">
-        <v>70.01905116866453</v>
+        <v>80.50287893608291</v>
       </c>
       <c r="J43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="K43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="L43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="M43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="N43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="O43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="P43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="Q43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="R43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="S43" t="n">
-        <v>77.49632980430073</v>
+        <v>147.5107198614164</v>
       </c>
       <c r="T43" t="n">
-        <v>62.32</v>
+        <v>132.3343900571157</v>
       </c>
       <c r="U43" t="n">
-        <v>105.9211926382866</v>
+        <v>132.3343900571157</v>
       </c>
       <c r="V43" t="n">
-        <v>101.7087580764521</v>
+        <v>128.1219554952811</v>
       </c>
       <c r="W43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="X43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="Y43" t="n">
-        <v>70.01905116866453</v>
+        <v>96.43224858749356</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>994.4648410973447</v>
+        <v>62.32</v>
       </c>
       <c r="C44" t="n">
-        <v>656.6117317609871</v>
+        <v>62.32</v>
       </c>
       <c r="D44" t="n">
-        <v>358.2893522257853</v>
+        <v>62.32</v>
       </c>
       <c r="E44" t="n">
-        <v>358.2893522257853</v>
+        <v>62.32</v>
       </c>
       <c r="F44" t="n">
-        <v>358.2893522257853</v>
+        <v>62.32</v>
       </c>
       <c r="G44" t="n">
-        <v>358.2893522257853</v>
+        <v>62.32</v>
       </c>
       <c r="H44" t="n">
         <v>62.32</v>
@@ -7648,13 +7648,13 @@
         <v>1543.236366347868</v>
       </c>
       <c r="M44" t="n">
-        <v>2054.085195076803</v>
+        <v>1906.190904947141</v>
       </c>
       <c r="N44" t="n">
-        <v>2667.305514851566</v>
+        <v>1906.190904947141</v>
       </c>
       <c r="O44" t="n">
-        <v>2677.400904947332</v>
+        <v>1906.190904947141</v>
       </c>
       <c r="P44" t="n">
         <v>2677.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3116</v>
       </c>
       <c r="R44" t="n">
-        <v>3116</v>
+        <v>2978.74889007243</v>
       </c>
       <c r="S44" t="n">
-        <v>3116</v>
+        <v>2978.74889007243</v>
       </c>
       <c r="T44" t="n">
-        <v>2639.560018455996</v>
+        <v>2502.308908528426</v>
       </c>
       <c r="U44" t="n">
-        <v>2099.942547194773</v>
+        <v>1962.691437267203</v>
       </c>
       <c r="V44" t="n">
-        <v>2099.942547194773</v>
+        <v>1442.639897704755</v>
       </c>
       <c r="W44" t="n">
-        <v>1571.282470446341</v>
+        <v>913.9798209563228</v>
       </c>
       <c r="X44" t="n">
-        <v>1089.179608364859</v>
+        <v>431.8769588748402</v>
       </c>
       <c r="Y44" t="n">
-        <v>1089.179608364859</v>
+        <v>431.8769588748402</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>281.6817042287082</v>
+        <v>289.2252952907847</v>
       </c>
       <c r="C45" t="n">
-        <v>281.6817042287082</v>
+        <v>289.2252952907847</v>
       </c>
       <c r="D45" t="n">
-        <v>281.6817042287082</v>
+        <v>289.2252952907847</v>
       </c>
       <c r="E45" t="n">
-        <v>281.6817042287082</v>
+        <v>289.2252952907847</v>
       </c>
       <c r="F45" t="n">
-        <v>281.6817042287082</v>
+        <v>62.32</v>
       </c>
       <c r="G45" t="n">
-        <v>281.6817042287082</v>
+        <v>62.32</v>
       </c>
       <c r="H45" t="n">
         <v>62.32</v>
@@ -7718,52 +7718,52 @@
         <v>62.32</v>
       </c>
       <c r="J45" t="n">
-        <v>300.126520175299</v>
+        <v>242.1274635715253</v>
       </c>
       <c r="K45" t="n">
-        <v>603.1693362696824</v>
+        <v>545.1702796659088</v>
       </c>
       <c r="L45" t="n">
-        <v>988.3697978648825</v>
+        <v>930.3707412611088</v>
       </c>
       <c r="M45" t="n">
-        <v>1188.300339607742</v>
+        <v>1130.301283003968</v>
       </c>
       <c r="N45" t="n">
-        <v>1435.43062421531</v>
+        <v>1263.581567611536</v>
       </c>
       <c r="O45" t="n">
-        <v>1754.44409475064</v>
+        <v>1616.474019295255</v>
       </c>
       <c r="P45" t="n">
-        <v>1866.973439220147</v>
+        <v>1842.853363764762</v>
       </c>
       <c r="Q45" t="n">
-        <v>1866.973439220147</v>
+        <v>1784.187439430944</v>
       </c>
       <c r="R45" t="n">
-        <v>1866.973439220147</v>
+        <v>1347.547240145713</v>
       </c>
       <c r="S45" t="n">
-        <v>1866.973439220147</v>
+        <v>1178.549400768652</v>
       </c>
       <c r="T45" t="n">
-        <v>1573.682767283264</v>
+        <v>885.2587288317688</v>
       </c>
       <c r="U45" t="n">
-        <v>1573.682767283264</v>
+        <v>597.1674563467318</v>
       </c>
       <c r="V45" t="n">
-        <v>1271.146739817082</v>
+        <v>597.1674563467318</v>
       </c>
       <c r="W45" t="n">
-        <v>1149.167248529565</v>
+        <v>597.1674563467318</v>
       </c>
       <c r="X45" t="n">
-        <v>841.2250874736184</v>
+        <v>289.2252952907847</v>
       </c>
       <c r="Y45" t="n">
-        <v>553.9610543765129</v>
+        <v>289.2252952907847</v>
       </c>
     </row>
     <row r="46">
@@ -7797,40 +7797,40 @@
         <v>62.32</v>
       </c>
       <c r="J46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="K46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="L46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="M46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="N46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="O46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="P46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="Q46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="R46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="S46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="T46" t="n">
-        <v>98.64160734793731</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="U46" t="n">
-        <v>62.32</v>
+        <v>141.2537406524513</v>
       </c>
       <c r="V46" t="n">
         <v>62.32</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>51.26150624509023</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>814.9999999999995</v>
+        <v>814.9999999999998</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>213.4717149255715</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q2" t="n">
-        <v>189.0411843274853</v>
+        <v>286.6924518804083</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1060.271045550332</v>
+        <v>512.2714279449685</v>
       </c>
       <c r="N5" t="n">
-        <v>883.0371884315879</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
         <v>885.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2870600406826043</v>
+        <v>761.4713325309352</v>
       </c>
       <c r="Q5" t="n">
-        <v>615.8520732695737</v>
+        <v>189.0411843274853</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>67.29211380696638</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8456,10 +8456,10 @@
         <v>885.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406814674</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q8" t="n">
-        <v>615.8520732695737</v>
+        <v>304.100956735474</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8684,19 +8684,19 @@
         <v>815</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>781.7521334878174</v>
       </c>
       <c r="N11" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>234.7583464536658</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,7 +8915,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8924,16 +8924,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>818.1445104262727</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
         <v>885.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>239.2082787301582</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>151.7858245236418</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
@@ -9170,7 +9170,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>337.3331612070587</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,22 +9389,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>815</v>
+        <v>242.7706698795373</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>307.7378754195927</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9623,28 +9623,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>758.7795877875526</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>885.2478695740924</v>
+        <v>630.0200767947325</v>
       </c>
       <c r="P23" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,19 +9863,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>234.3500978109578</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>402.058620489197</v>
       </c>
       <c r="P26" t="n">
         <v>779.2870600407069</v>
@@ -10097,22 +10097,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>727.0724812561642</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N29" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>820.6068852930586</v>
       </c>
       <c r="P29" t="n">
         <v>779.2870600407135</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
@@ -10343,19 +10343,19 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>911.8541914946812</v>
       </c>
       <c r="N32" t="n">
-        <v>429.4103365460504</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>796.4372956432948</v>
+        <v>849.2478695741381</v>
       </c>
       <c r="P32" t="n">
         <v>779.2870600407272</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,7 +10574,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10586,13 +10586,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>465.1548207585124</v>
+        <v>846.0593272236316</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600407517</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,22 +10811,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>716.8751175230994</v>
+        <v>689.2054510345541</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>465.4418807994419</v>
+        <v>849.2478695741827</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>779.2870600407717</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,22 +11048,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>172.2252153338092</v>
       </c>
       <c r="L41" t="n">
-        <v>393.9356333920305</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>849.2478695742291</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600408181</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11291,16 +11291,16 @@
         <v>778.9999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>910.8828737021881</v>
       </c>
       <c r="N44" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
-        <v>80.44523330718953</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600408754</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -23238,10 +23238,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23283,16 +23283,16 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>103.7292154737334</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>49.37954299166896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23426,10 +23426,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>160.0624669370704</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23654,19 +23654,19 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>292.1850752716849</v>
+        <v>275.8376408970016</v>
       </c>
       <c r="O16" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>108.2004986247733</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>83.37347970285543</v>
@@ -23897,13 +23897,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>69.8091295274528</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>69.04626797189968</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -24128,19 +24128,19 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>314.229009994322</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24371,13 +24371,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>69.04626797189968</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>11.77810239760592</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24456,7 +24456,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -24468,13 +24468,13 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>230.4082714921873</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24654,13 +24654,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>64.60194891603</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>127.4007821087353</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H29" t="n">
         <v>157.0096587035274</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>243.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24848,10 +24848,10 @@
         <v>436.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>421.860847251041</v>
       </c>
       <c r="R31" t="n">
-        <v>421.8608472510409</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>111.3734797028554</v>
@@ -24885,7 +24885,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>10.25860861458554</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>10.25860861458553</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -25067,28 +25067,28 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.5207738011430365</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>135.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>184.7465968181318</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>283.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>352.445564079015</v>
       </c>
       <c r="P34" t="n">
         <v>399.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>437.839266425598</v>
+        <v>56.85733851270868</v>
       </c>
       <c r="R34" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25170,13 +25170,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>10.25860861458523</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>10.25860861458591</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -25316,19 +25316,19 @@
         <v>283.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>352.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>295.7751922359946</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>74.37347970285543</v>
+        <v>56.85733851270872</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25553,19 +25553,19 @@
         <v>283.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>352.445564079015</v>
+        <v>295.7751922359946</v>
       </c>
       <c r="P40" t="n">
-        <v>399.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>56.85733851270872</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>57.30352415461198</v>
       </c>
       <c r="C41" t="n">
         <v>254.4745782429939</v>
@@ -25641,10 +25641,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>55.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.42492532631735</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25720,16 +25720,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>181.9156543808848</v>
+        <v>352.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>53.96794860432524</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>205.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -25769,7 +25769,7 @@
         <v>50.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>33.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>273.2316933607354</v>
+        <v>1.137923669482689</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>334.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>295.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>289.3632896068686</v>
@@ -25848,7 +25848,7 @@
         <v>288.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>293.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>35.08115968268461</v>
@@ -25878,7 +25878,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>135.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>379.8481678023229</v>
@@ -25890,7 +25890,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>514.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>269.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>246.0999124455193</v>
@@ -25921,13 +25921,13 @@
         <v>227.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>224.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>210.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>217.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>102.1263858913485</v>
@@ -25954,31 +25954,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>58.07926509047959</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>432.2737972923793</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>351.5639999646113</v>
+        <v>184.2561389813208</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>285.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>299.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>196.6134465351867</v>
+        <v>317.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>284.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -26045,10 +26045,10 @@
         <v>95.02456650625771</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>35.95839127445794</v>
       </c>
       <c r="V46" t="n">
-        <v>84.17031021621619</v>
+        <v>6.025906970289384</v>
       </c>
       <c r="W46" t="n">
         <v>111.3728098387097</v>
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4578082.979918787</v>
+        <v>4578082.979918786</v>
       </c>
     </row>
     <row r="7">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6345908.870006283</v>
+        <v>6345908.870006282</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7229821.81505003</v>
+        <v>7229821.815050028</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8035233.902773301</v>
+        <v>8035233.902773298</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8877059.272462286</v>
+        <v>8877059.272462284</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9764121.800085919</v>
+        <v>9764121.800085917</v>
       </c>
     </row>
     <row r="13">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11538204.33104028</v>
+        <v>11538204.33104027</v>
       </c>
     </row>
     <row r="15">
@@ -26272,10 +26272,10 @@
         <v>1290861.466340909</v>
       </c>
       <c r="C2" t="n">
-        <v>1290861.466340909</v>
+        <v>1290861.46634091</v>
       </c>
       <c r="D2" t="n">
-        <v>1290861.466340909</v>
+        <v>1290861.46634091</v>
       </c>
       <c r="E2" t="n">
         <v>1154496.382945596</v>
@@ -26287,10 +26287,10 @@
         <v>1249670.025751511</v>
       </c>
       <c r="H2" t="n">
-        <v>1249670.02575151</v>
+        <v>1249670.025751511</v>
       </c>
       <c r="I2" t="n">
-        <v>1249670.02575151</v>
+        <v>1249670.025751511</v>
       </c>
       <c r="J2" t="n">
         <v>1143097.541953596</v>
@@ -26299,10 +26299,10 @@
         <v>1190166.901974092</v>
       </c>
       <c r="L2" t="n">
+        <v>1254092.823605639</v>
+      </c>
+      <c r="M2" t="n">
         <v>1254092.823605638</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1254092.823605639</v>
       </c>
       <c r="N2" t="n">
         <v>1254092.823605668</v>
@@ -26311,7 +26311,7 @@
         <v>1057481.429618646</v>
       </c>
       <c r="P2" t="n">
-        <v>828160.5174519989</v>
+        <v>828160.5174519982</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575920.3474495771</v>
+        <v>580809.5038374889</v>
       </c>
       <c r="C4" t="n">
-        <v>574167.5049491362</v>
+        <v>579056.661337048</v>
       </c>
       <c r="D4" t="n">
-        <v>572412.2846084387</v>
+        <v>577301.4409963507</v>
       </c>
       <c r="E4" t="n">
-        <v>493973.8046613694</v>
+        <v>498813.3005071199</v>
       </c>
       <c r="F4" t="n">
-        <v>544553.626856441</v>
+        <v>549393.1227021916</v>
       </c>
       <c r="G4" t="n">
-        <v>542883.6451658958</v>
+        <v>547723.1410116465</v>
       </c>
       <c r="H4" t="n">
-        <v>541211.3456360602</v>
+        <v>546050.8414818107</v>
       </c>
       <c r="I4" t="n">
-        <v>539536.7115489381</v>
+        <v>544376.2073946884</v>
       </c>
       <c r="J4" t="n">
-        <v>483585.363292172</v>
+        <v>488315.773108913</v>
       </c>
       <c r="K4" t="n">
-        <v>507320.6786559278</v>
+        <v>512051.0884726688</v>
       </c>
       <c r="L4" t="n">
-        <v>539876.9064614968</v>
+        <v>544608.0596004378</v>
       </c>
       <c r="M4" t="n">
-        <v>538156.9451324799</v>
+        <v>542888.098271421</v>
       </c>
       <c r="N4" t="n">
-        <v>536434.5107850994</v>
+        <v>541165.6639240405</v>
       </c>
       <c r="O4" t="n">
-        <v>430730.7840429268</v>
+        <v>435461.1938596678</v>
       </c>
       <c r="P4" t="n">
-        <v>308208.0261529455</v>
+        <v>312938.4359696866</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>344881.5188913324</v>
+        <v>339992.3625034206</v>
       </c>
       <c r="C6" t="n">
-        <v>633514.3613917733</v>
+        <v>628625.2050038617</v>
       </c>
       <c r="D6" t="n">
-        <v>635269.5817324708</v>
+        <v>630380.4253445592</v>
       </c>
       <c r="E6" t="n">
-        <v>412055.0532842266</v>
+        <v>407215.5574384764</v>
       </c>
       <c r="F6" t="n">
-        <v>588909.1478950693</v>
+        <v>584069.6520493188</v>
       </c>
       <c r="G6" t="n">
-        <v>633779.129585615</v>
+        <v>628939.6337398641</v>
       </c>
       <c r="H6" t="n">
-        <v>635451.4291154499</v>
+        <v>630611.9332696999</v>
       </c>
       <c r="I6" t="n">
-        <v>637126.0632025723</v>
+        <v>632286.5673568222</v>
       </c>
       <c r="J6" t="n">
-        <v>182225.4536614243</v>
+        <v>177495.0438446831</v>
       </c>
       <c r="K6" t="n">
-        <v>550381.7043181643</v>
+        <v>545651.2945014228</v>
       </c>
       <c r="L6" t="n">
-        <v>613040.8451441407</v>
+        <v>608309.6920052009</v>
       </c>
       <c r="M6" t="n">
-        <v>644360.806473159</v>
+        <v>639629.6533342167</v>
       </c>
       <c r="N6" t="n">
-        <v>646083.2408205684</v>
+        <v>641352.0876816279</v>
       </c>
       <c r="O6" t="n">
-        <v>500593.9905757194</v>
+        <v>495863.5807589784</v>
       </c>
       <c r="P6" t="n">
-        <v>462921.3562990534</v>
+        <v>458190.9464823116</v>
       </c>
     </row>
   </sheetData>
@@ -26987,10 +26987,10 @@
         <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27005,7 +27005,7 @@
         <v>37</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27448,52 +27448,52 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>250.8785988282945</v>
+      </c>
+      <c r="S2" t="n">
+        <v>52.63096829726999</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>400</v>
       </c>
-      <c r="H2" t="n">
-        <v>303.5095671255648</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>400</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>400</v>
@@ -27530,7 +27530,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>341.6657683827116</v>
+        <v>47.52172789347793</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27575,13 +27575,13 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27603,7 +27603,7 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
@@ -27612,10 +27612,10 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>314.1276222272376</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>150.9583912744579</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>325.6395755681846</v>
       </c>
     </row>
     <row r="5">
@@ -27670,25 +27670,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>302.549808614586</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -27721,10 +27721,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>302.5498086145852</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27739,7 +27739,7 @@
         <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -27758,7 +27758,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>275.1521238203181</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27812,13 +27812,13 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>284.3378656046244</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27840,10 +27840,10 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27885,19 +27885,19 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>302.0188136561015</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>280.0293020277298</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27919,52 +27919,52 @@
         <v>400</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>303.5095671255647</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>400</v>
       </c>
-      <c r="G8" t="n">
+      <c r="T8" t="n">
         <v>400</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>250.8785988282945</v>
-      </c>
-      <c r="S8" t="n">
-        <v>52.63096829726999</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27973,7 +27973,7 @@
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y8" t="n">
         <v>400</v>
@@ -27986,25 +27986,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>224.5827151763668</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>206.9367063470277</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,34 +28065,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
         <v>400</v>
       </c>
-      <c r="G10" t="n">
-        <v>245.04387284153</v>
-      </c>
       <c r="H10" t="n">
-        <v>247.4193345185975</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
-        <v>35.26894883590776</v>
+        <v>236.423940235454</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28119,10 +28119,10 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
@@ -28131,10 +28131,10 @@
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28253,13 +28253,13 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>19.11687125883935</v>
+        <v>225</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>19.11687125883935</v>
       </c>
       <c r="O12" t="n">
         <v>225</v>
@@ -28387,7 +28387,7 @@
         <v>279</v>
       </c>
       <c r="D14" t="n">
-        <v>275.549808614586</v>
+        <v>279</v>
       </c>
       <c r="E14" t="n">
         <v>279</v>
@@ -28402,7 +28402,7 @@
         <v>279</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6309682972706</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28487,7 +28487,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>155.670590267103</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -28496,13 +28496,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="O15" t="n">
-        <v>155.6705902671029</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>279</v>
@@ -28718,19 +28718,19 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>217.5442043757545</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>279</v>
+        <v>261.5913251766235</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28858,7 +28858,7 @@
         <v>279</v>
       </c>
       <c r="C20" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="D20" t="n">
         <v>279</v>
@@ -28876,7 +28876,7 @@
         <v>279</v>
       </c>
       <c r="I20" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28958,7 +28958,7 @@
         <v>279</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>155.670590267103</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -28967,16 +28967,16 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>279</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29110,7 +29110,7 @@
         <v>279</v>
       </c>
       <c r="H23" t="n">
-        <v>275.549808614586</v>
+        <v>279</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29192,31 +29192,31 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
+        <v>261.5913251766233</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>279</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>155.6705902671029</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29429,7 +29429,7 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
         <v>225</v>
@@ -29438,7 +29438,7 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>26.99048536749045</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29672,25 +29672,25 @@
         <v>251</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="L30" t="n">
         <v>251</v>
       </c>
       <c r="M30" t="n">
-        <v>166.1982915220771</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>244.1190264315981</v>
       </c>
       <c r="O30" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>251</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>251</v>
@@ -29903,31 +29903,31 @@
         <v>288</v>
       </c>
       <c r="I33" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J33" t="n">
         <v>288</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>61.80315754379842</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>288</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>105.8502783446676</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>288</v>
@@ -30140,20 +30140,20 @@
         <v>288</v>
       </c>
       <c r="I36" t="n">
+        <v>278.9295434351469</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>288</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
@@ -30161,7 +30161,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>278.929543435147</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>288</v>
@@ -30377,10 +30377,10 @@
         <v>288</v>
       </c>
       <c r="I39" t="n">
+        <v>278.929543435147</v>
+      </c>
+      <c r="J39" t="n">
         <v>288</v>
-      </c>
-      <c r="J39" t="n">
-        <v>278.929543435147</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30626,7 +30626,7 @@
         <v>195</v>
       </c>
       <c r="M42" t="n">
-        <v>195</v>
+        <v>83.94080612010359</v>
       </c>
       <c r="N42" t="n">
         <v>195</v>
@@ -30635,10 +30635,10 @@
         <v>195</v>
       </c>
       <c r="P42" t="n">
-        <v>81.52392975117381</v>
+        <v>195</v>
       </c>
       <c r="Q42" t="n">
-        <v>195</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
         <v>195</v>
@@ -30693,10 +30693,10 @@
         <v>195</v>
       </c>
       <c r="I43" t="n">
-        <v>176.6334556201183</v>
+        <v>195</v>
       </c>
       <c r="J43" t="n">
-        <v>42.82175553857059</v>
+        <v>102.9536366392749</v>
       </c>
       <c r="K43" t="n">
         <v>195</v>
@@ -30729,7 +30729,7 @@
         <v>195</v>
       </c>
       <c r="U43" t="n">
-        <v>195</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
         <v>195</v>
@@ -30854,7 +30854,7 @@
         <v>115</v>
       </c>
       <c r="J45" t="n">
-        <v>115</v>
+        <v>56.41509433962264</v>
       </c>
       <c r="K45" t="n">
         <v>115</v>
@@ -30866,13 +30866,13 @@
         <v>115</v>
       </c>
       <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
         <v>115</v>
       </c>
-      <c r="O45" t="n">
-        <v>80.77880692081989</v>
-      </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="Q45" t="n">
         <v>115</v>
@@ -30933,7 +30933,7 @@
         <v>115</v>
       </c>
       <c r="J46" t="n">
-        <v>71.95744110655153</v>
+        <v>115</v>
       </c>
       <c r="K46" t="n">
         <v>115</v>
@@ -34746,10 +34746,10 @@
         <v>815</v>
       </c>
       <c r="K2" t="n">
-        <v>783.0093003026486</v>
+        <v>783.0093003026041</v>
       </c>
       <c r="L2" t="n">
-        <v>815</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>815</v>
@@ -34889,7 +34889,7 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
@@ -34898,10 +34898,10 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>137.4941666071192</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>111.479226198857</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>38.17422271872228</v>
       </c>
     </row>
     <row r="5">
@@ -34986,10 +34986,10 @@
         <v>815</v>
       </c>
       <c r="L5" t="n">
-        <v>783.0093003026393</v>
+        <v>815</v>
       </c>
       <c r="M5" t="n">
-        <v>815</v>
+        <v>783.0093003026512</v>
       </c>
       <c r="N5" t="n">
         <v>815</v>
@@ -34998,7 +34998,7 @@
         <v>815</v>
       </c>
       <c r="P5" t="n">
-        <v>815.0000000000011</v>
+        <v>815</v>
       </c>
       <c r="Q5" t="n">
         <v>815</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35126,10 +35126,10 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35171,19 +35171,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>151.0604223816436</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>53.65649218902013</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,7 +35220,7 @@
         <v>815</v>
       </c>
       <c r="K8" t="n">
-        <v>783.0093003026083</v>
+        <v>783.0093003026252</v>
       </c>
       <c r="L8" t="n">
         <v>815</v>
@@ -35229,7 +35229,7 @@
         <v>815</v>
       </c>
       <c r="N8" t="n">
-        <v>815</v>
+        <v>815.0000000000011</v>
       </c>
       <c r="O8" t="n">
         <v>815</v>
@@ -35351,34 +35351,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>18.64820841697891</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>201.1549913995462</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35405,10 +35405,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
@@ -35417,10 +35417,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35463,19 +35463,19 @@
         <v>815</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>237.4900058455002</v>
       </c>
       <c r="N11" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>164.5104768795733</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35539,13 +35539,13 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>293.2082466075263</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>359.6265501086548</v>
+        <v>153.7434213674942</v>
       </c>
       <c r="O12" t="n">
         <v>466.4570219027464</v>
@@ -35694,7 +35694,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -35703,16 +35703,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>340.8955523564375</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
         <v>815</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>66.38559440267282</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35773,7 +35773,7 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>346.7744449078943</v>
       </c>
       <c r="L15" t="n">
         <v>274.091375348687</v>
@@ -35782,13 +35782,13 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N15" t="n">
-        <v>134.6265501086548</v>
+        <v>413.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>397.1276121698493</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>105.9207349095204</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>116.7428182785515</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
         <v>815</v>
@@ -35949,7 +35949,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>164.5104768795733</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,19 +36004,19 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K18" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>491.6355797244415</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>365.9500421645043</v>
+        <v>348.5413673411278</v>
       </c>
       <c r="N18" t="n">
         <v>134.6265501086548</v>
@@ -36028,7 +36028,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36168,22 +36168,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>242.7706698795373</v>
+      </c>
+      <c r="M20" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>815</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>619.4144644189528</v>
-      </c>
-      <c r="O20" t="n">
-        <v>237.4900058455002</v>
-      </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36244,7 +36244,7 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>125.2086062376757</v>
+        <v>280.8791965047787</v>
       </c>
       <c r="K21" t="n">
         <v>191.1038546407913</v>
@@ -36253,16 +36253,16 @@
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N21" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>397.1276121698494</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36402,28 +36402,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>758.7795877875526</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>815</v>
+        <v>559.77220722064</v>
       </c>
       <c r="P23" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36478,31 +36478,31 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>61.87361410865147</v>
+        <v>44.46493928527482</v>
       </c>
       <c r="J24" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M24" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>290.2971403757577</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36642,19 +36642,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>234.3500978109578</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>331.8107509151045</v>
       </c>
       <c r="P26" t="n">
         <v>779.0000000000255</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>350.2086062376757</v>
@@ -36724,7 +36724,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>293.2082466075261</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>140.6564898821437</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36876,22 +36876,22 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L29" t="n">
-        <v>727.0724812561642</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>750.3590157189661</v>
       </c>
       <c r="P29" t="n">
         <v>779.0000000000321</v>
@@ -36958,25 +36958,25 @@
         <v>376.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>191.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L30" t="n">
         <v>525.0913753486871</v>
       </c>
       <c r="M30" t="n">
-        <v>253.1483336865814</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N30" t="n">
-        <v>134.6265501086548</v>
+        <v>378.7455765402529</v>
       </c>
       <c r="O30" t="n">
-        <v>492.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P30" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>77.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>47.83862152372274</v>
       </c>
       <c r="M32" t="n">
-        <v>516.0089179080152</v>
+        <v>367.5920638523639</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>726.1894260692023</v>
+        <v>779.0000000000457</v>
       </c>
       <c r="P32" t="n">
         <v>779.0000000000457</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,22 +37189,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>70.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>413.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>562.0913753486871</v>
+        <v>335.8945328924854</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>240.4768284533224</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
@@ -37213,7 +37213,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>114.9207349095204</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37353,10 +37353,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>764.7137390467662</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>47.83862152375355</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
@@ -37365,13 +37365,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O35" t="n">
-        <v>394.90695118442</v>
+        <v>775.8114576495392</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>779.0000000000703</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>70.87361410865147</v>
+        <v>61.80315754379838</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37438,7 +37438,7 @@
         <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
-        <v>86.95004216450428</v>
+        <v>374.9500421645043</v>
       </c>
       <c r="N36" t="n">
         <v>134.6265501086548</v>
@@ -37447,7 +37447,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>392.5955479498002</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
         <v>114.9207349095204</v>
@@ -37590,22 +37590,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>764.4266790182833</v>
+        <v>737.0440725703991</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>395.1940112253495</v>
+        <v>779.0000000000903</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>779.0000000000903</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37663,10 +37663,10 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>70.87361410865147</v>
+        <v>61.80315754379851</v>
       </c>
       <c r="J39" t="n">
-        <v>404.1381496728227</v>
+        <v>413.2086062376757</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37827,22 +37827,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230996</v>
+        <v>172.2252153338092</v>
       </c>
       <c r="L41" t="n">
-        <v>393.9356333920305</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>779.0000000001367</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>779.0000000001367</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37912,7 +37912,7 @@
         <v>469.091375348687</v>
       </c>
       <c r="M42" t="n">
-        <v>281.9500421645043</v>
+        <v>170.8908482846079</v>
       </c>
       <c r="N42" t="n">
         <v>329.6265501086548</v>
@@ -37921,10 +37921,10 @@
         <v>436.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>195.189934265827</v>
+        <v>308.6660045146532</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>18.36654437988173</v>
       </c>
       <c r="J43" t="n">
-        <v>7.552806702662824</v>
+        <v>67.68468780336713</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>44.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38070,16 +38070,16 @@
         <v>778.9999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>366.6207460598708</v>
       </c>
       <c r="N44" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>10.19736373309708</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>779.0000000001939</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>240.2086062376757</v>
+        <v>181.6237005772983</v>
       </c>
       <c r="K45" t="n">
         <v>306.1038546407913</v>
@@ -38152,13 +38152,13 @@
         <v>201.9500421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>249.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>322.2358288235663</v>
+        <v>356.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>113.6660045146532</v>
+        <v>228.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>36.68849227064375</v>
+        <v>79.73105116409224</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
